--- a/Result/profitability/3014.xlsx
+++ b/Result/profitability/3014.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.17</v>
       </c>
       <c r="M2" t="n">
-        <v>2.3325</v>
+        <v>2.32625</v>
       </c>
       <c r="N2" t="n">
-        <v>53.6825</v>
+        <v>53.79875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.92</v>
       </c>
       <c r="M3" t="n">
-        <v>2.0625</v>
+        <v>2.18375</v>
       </c>
       <c r="N3" t="n">
-        <v>51.22375</v>
+        <v>51.4425</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.16</v>
       </c>
       <c r="M4" t="n">
-        <v>1.95</v>
+        <v>1.975</v>
       </c>
       <c r="N4" t="n">
-        <v>49.20625</v>
+        <v>49.21</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.25</v>
       </c>
       <c r="M5" t="n">
-        <v>1.6275</v>
+        <v>1.71125</v>
       </c>
       <c r="N5" t="n">
-        <v>46.58125</v>
+        <v>46.975</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.73</v>
       </c>
       <c r="M6" t="n">
-        <v>1.42375</v>
+        <v>1.49875</v>
       </c>
       <c r="N6" t="n">
-        <v>44.99125</v>
+        <v>45.50625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.53</v>
       </c>
       <c r="M7" t="n">
-        <v>1.18625</v>
+        <v>1.33</v>
       </c>
       <c r="N7" t="n">
-        <v>43.42125</v>
+        <v>43.49</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,7 +1391,7 @@
         <v>0.79</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>1.0725</v>
       </c>
       <c r="N8" t="n">
         <v>41.435</v>
@@ -1645,7 +1645,7 @@
         <v>0.62</v>
       </c>
       <c r="M10" t="n">
-        <v>0.67375</v>
+        <v>0.6737500000000001</v>
       </c>
       <c r="N10" t="n">
         <v>39.21</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3014</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1835</v>
+      </c>
+      <c r="D75" t="n">
+        <v>785</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F75" t="n">
+        <v>57.21</v>
+      </c>
+      <c r="G75" t="n">
+        <v>518</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>28.24%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>82</v>
+      </c>
+      <c r="J75" t="n">
+        <v>601</v>
+      </c>
+      <c r="K75" t="n">
+        <v>488</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="N75" t="n">
+        <v>55.89375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.1799999999999997</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.06315789473684208</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.6699999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.2838983050847457</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.149999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.05826859045504995</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
